--- a/tests/data/TEST.xlsx
+++ b/tests/data/TEST.xlsx
@@ -421,8 +421,9 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="75.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
